--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.54</v>
+        <v>33.43</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.6</v>
+        <v>30.67</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>52.7</v>
+        <v>48.3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=52.7中性区</t>
+          <t>价格站上60日均线；RSI=48.3中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>56.36</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.37</v>
+        <v>54.52</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.56</v>
+        <v>52.6</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.9超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=73.7中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,109 +609,109 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>348.20</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.21</v>
+        <v>376.99</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.66</v>
+        <v>381.54</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.7</v>
+        <v>15.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>344.76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>412.64</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=59.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.8超卖区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>351.00</t>
+          <t>41.07</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>379.27</v>
+        <v>39.59</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>382.3</v>
+        <v>38.25</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>344.76</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.6超卖区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1330.00</t>
+          <t>1316.01</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1311.28</v>
+        <v>1309.63</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1270.43</v>
+        <v>1271.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.6</v>
+        <v>56.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=63.6中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,58 +762,58 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39.48</v>
+        <v>28.2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38.2</v>
+        <v>27.66</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>84</v>
+        <v>45.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.0超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=45.1中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>86.27</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.58</v>
+        <v>85.63</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.23999999999999</v>
+        <v>82.36</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>75.7</v>
+        <v>63.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.7超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=63.5中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4.77</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27</v>
+        <v>31.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=27.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.2超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.43</v>
+        <v>33.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.67</v>
+        <v>30.73</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>48.3</v>
+        <v>59.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=48.3中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>55.70</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.52</v>
+        <v>54.68</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.6</v>
+        <v>52.62</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>73.7</v>
+        <v>67.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=73.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,148 +609,148 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>348.20</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>376.99</v>
+        <v>28.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>381.54</v>
+        <v>27.68</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15.8</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>344.76</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.8超卖区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.07</t>
+          <t>335.49</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39.59</v>
+        <v>374.24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38.25</v>
+        <v>380.52</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>412.64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1316.01</t>
+          <t>40.90</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1309.63</v>
+        <v>39.69</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1271.3</v>
+        <v>38.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>56.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27.66</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45.1</v>
+        <v>52.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=45.1中性区</t>
+          <t>价格站上60日均线；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>1309.30</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.63</v>
+        <v>1307.78</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.36</v>
+        <v>1272.4</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>63.5</v>
+        <v>50.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>1151.01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=63.5中性区</t>
+          <t>价格站上60日均线；RSI=50.5中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.77</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>31.2</v>
+        <v>44.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>34.40</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.48</v>
+        <v>33.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.73</v>
+        <v>30.81</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>59.4</v>
+        <v>54</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=54.0中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>55.70</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.68</v>
+        <v>54.86</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.62</v>
+        <v>52.68</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.7中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,160 +609,160 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>336.84</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.18</v>
+        <v>371.39</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.68</v>
+        <v>379.43</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>39</v>
+        <v>17.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>412.64</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.1超卖区；近20日已跌-14.5%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>335.49</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>374.24</v>
+        <v>39.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>380.52</v>
+        <v>38.36</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=72.4中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.90</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39.69</v>
+        <v>28.18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38.3</v>
+        <v>27.71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>价格站上60日均线；RSI=47.7中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>85.69</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.67</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=52.2中性区</t>
+          <t>价格站上60日均线；RSI=53.1中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1309.30</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1307.78</v>
+        <v>55.96</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1272.4</v>
+        <v>59.96</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.5</v>
+        <v>58.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=50.5中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=58.8中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>44.7</v>
+        <v>47.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=47.3中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>34.40</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.55</v>
+        <v>33.66</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>54</v>
+        <v>45.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=54.0中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,148 +558,148 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>338.06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.86</v>
+        <v>368.47</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.68</v>
+        <v>378.44</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>68.7</v>
+        <v>11.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>46.90</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>58.99</t>
+          <t>412.64</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=11.1超卖区；近20日已跌-14.7%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>336.84</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>371.39</v>
+        <v>28.17</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>379.43</v>
+        <v>27.74</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17.1</v>
+        <v>52.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.1超卖区；近20日已跌-14.5%，接近超跌</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>1285.13</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39.8</v>
+        <v>1301.66</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38.36</v>
+        <v>1274.67</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>1151.01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=72.4中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,58 +711,58 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.18</v>
+        <v>39.94</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27.71</v>
+        <v>38.43</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>47.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=47.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>86.20</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.69</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>82.67</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>53.1</v>
+        <v>60.3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=53.1中性区</t>
+          <t>价格站上60日均线；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55.96</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>59.96</v>
+        <v>52.72</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>58.8</v>
+        <v>60.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>46.90</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76.16</t>
+          <t>58.99</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=58.8中性区</t>
+          <t>价格站上60日均线；MACD死叉；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.76</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>47.3</v>
+        <v>39.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=47.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.5中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -665,46 +665,46 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1285.13</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1301.66</v>
+        <v>54.07</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1274.67</v>
+        <v>51.76</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>54.7</v>
+        <v>65.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
+          <t>价格站上60日均线；RSI=65.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -716,41 +716,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>1285.13</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39.94</v>
+        <v>1301.66</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38.43</v>
+        <v>1274.67</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>54.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>1151.01</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,46 +767,46 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.20</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.79000000000001</v>
+        <v>39.94</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>38.43</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>60.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=60.3中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
@@ -818,41 +818,41 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>86.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52.72</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>60.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46.90</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.99</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD死叉；RSI=60.3中性区</t>
+          <t>价格站上60日均线；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
         <v>4.76</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.5</v>
+        <v>39.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,12 +903,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.5中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=39.1中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.66</v>
+        <v>33.65</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.89</v>
+        <v>30.94</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45.2</v>
+        <v>34.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=45.2中性区</t>
+          <t>价格站上60日均线；RSI=34.5超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>338.06</t>
+          <t>330.70</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>368.47</v>
+        <v>365.31</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>378.44</v>
+        <v>377.45</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=11.1超卖区；近20日已跌-14.7%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-16.1%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.17</v>
+        <v>28.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.74</v>
+        <v>27.78</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=52.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,97 +660,97 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.07</v>
+        <v>85.95</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>51.76</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>65.7</v>
+        <v>51.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=65.7中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1285.13</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1301.66</v>
+        <v>40.08</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1274.67</v>
+        <v>38.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.7</v>
+        <v>66.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=66.2中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,109 +762,109 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>54.54</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39.94</v>
+        <v>54.26</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38.43</v>
+        <v>51.86</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
+          <t>价格站上60日均线；MACD死叉；RSI=53.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86.20</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.79000000000001</v>
+        <v>55.77</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>60.3</v>
+        <v>52.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=60.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=52.8中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.1</v>
+        <v>38.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=39.1中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.6中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.65</v>
+        <v>33.67</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>30.94</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34.5</v>
+        <v>35.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,12 +546,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=34.5超卖区</t>
+          <t>价格站上60日均线；RSI=35.9中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.18</v>
+        <v>28.19</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>27.78</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>52</v>
+        <v>57.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=52.0中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>85.95</v>
+        <v>85.98</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>83.04000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.6</v>
+        <v>54.9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.54</t>
+          <t>55.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54.26</v>
+        <v>54.29</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>51.86</v>
+        <v>51.87</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>53.2</v>
+        <v>56.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD死叉；RSI=53.2中性区</t>
+          <t>价格站上60日均线；MACD死叉；RSI=56.8中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -889,11 +889,11 @@
         <v>4.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -532,7 +532,7 @@
         <v>30.94</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=35.9中性区</t>
+          <t>价格站上60日均线；RSI=36.1中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -573,11 +573,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>330.70</t>
+          <t>330.51</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>365.31</v>
+        <v>365.3</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>377.45</v>
@@ -624,7 +624,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -634,7 +634,7 @@
         <v>27.78</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>57.4</v>
+        <v>56.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>85.98</v>
+        <v>85.95</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>83.05</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>54.9</v>
+        <v>51.8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=54.9中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=51.8中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.08</v>
+        <v>40.09</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>38.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>66.2</v>
+        <v>68.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=66.2中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.2中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,41 +767,41 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54.29</v>
+        <v>55.82</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>51.87</v>
+        <v>59.51</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD死叉；RSI=56.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=55.8中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -818,46 +818,46 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>54.83</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55.77</v>
+        <v>54.27</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>59.5</v>
+        <v>51.86</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>52.8</v>
+        <v>54.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76.16</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=52.8中性区</t>
+          <t>价格站上60日均线；MACD死叉；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>38.8</v>
+        <v>41.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=41.2中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
